--- a/contents/assets/CXO-12/完成版TrendStyleJapan-SalesData.xlsx
+++ b/contents/assets/CXO-12/完成版TrendStyleJapan-SalesData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takujis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoftapc-my.sharepoint.com/personal/takujis_microsoft_com/Documents/Private Documents/OD_Partner/Partner/大塚商会/GP体験会/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91785615-DC41-4F26-ACE3-821B0DC93468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{91785615-DC41-4F26-ACE3-821B0DC93468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF34A62-6AB2-43DE-A038-9B1AEFB34BCF}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,10 @@
     <sheet name="商品カテゴリマスタ" sheetId="6" r:id="rId6"/>
     <sheet name="MarketData" sheetId="7" r:id="rId7"/>
     <sheet name="投資優先度" sheetId="8" r:id="rId8"/>
-    <sheet name="エグゼクティブサマリー" sheetId="9" r:id="rId9"/>
+    <sheet name="役員会サマリー" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">エグゼクティブサマリー!$A$1:$N$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">役員会サマリー!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -859,8 +859,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="\¥#,##0"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="182" formatCode="0.0"/>
-    <numFmt numFmtId="183" formatCode="0.00&quot;億円&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
+    <numFmt numFmtId="179" formatCode="0.00&quot;億円&quot;"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1264,7 +1264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1335,58 +1335,35 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1400,51 +1377,54 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="17" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1455,7 +1435,7 @@
     <xf numFmtId="177" fontId="24" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1476,7 +1456,7 @@
     <xf numFmtId="177" fontId="26" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1491,11 +1471,25 @@
     <xf numFmtId="0" fontId="26" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1657,7 +1651,7 @@
       <font>
         <name val="Yu Gothic"/>
       </font>
-      <numFmt numFmtId="178" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="180" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -5798,10 +5792,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D3F6000C-66FE-4667-97FE-AD557CF5DA68}" name="SalesData" displayName="SalesData" ref="A2:K2162" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:K2162" xr:uid="{D3F6000C-66FE-4667-97FE-AD557CF5DA68}"/>
@@ -6171,11 +6161,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
     </row>
     <row r="2" spans="1:3" ht="17.649999999999999">
       <c r="A2" s="23"/>
@@ -6190,11 +6180,11 @@
       <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="74.25" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
     </row>
     <row r="5" spans="1:3" ht="17.649999999999999">
       <c r="A5" s="23"/>
@@ -6444,19 +6434,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
     </row>
     <row r="2" spans="1:11" ht="17.649999999999999">
       <c r="A2" s="1" t="s">
@@ -82121,17 +82111,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:9" ht="17.649999999999999">
       <c r="A2" s="11" t="s">
@@ -82481,17 +82471,17 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="24" customHeight="1">
-      <c r="A14" s="59" t="s">
+      <c r="A14" s="83" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
     </row>
     <row r="15" spans="1:9" ht="17.649999999999999">
       <c r="A15" s="1"/>
@@ -82586,17 +82576,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:9" ht="17.649999999999999">
       <c r="A2" s="11" t="s">
@@ -82917,15 +82907,15 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
@@ -83159,18 +83149,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
     </row>
     <row r="2" spans="1:10" ht="17.649999999999999">
       <c r="A2" s="1" t="s">
@@ -83711,15 +83701,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
     </row>
     <row r="2" spans="1:7" ht="17.649999999999999">
       <c r="A2" s="1" t="s">
@@ -83910,19 +83900,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="82" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
     </row>
     <row r="2" spans="1:11" ht="17.649999999999999">
       <c r="A2" s="1" t="s">
@@ -84619,651 +84609,651 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="85" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
     </row>
     <row r="3" spans="1:16" ht="30" customHeight="1">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
     </row>
     <row r="4" spans="1:16" ht="46.05" customHeight="1">
-      <c r="A4" s="45">
+      <c r="A4" s="37">
         <v>1</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="38">
         <f>INDEX($K$9:$K$14,MATCH(B4,$A$9:$A$14,0))</f>
         <v>3.8</v>
       </c>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
     </row>
     <row r="5" spans="1:16" ht="46.05" customHeight="1">
-      <c r="A5" s="45">
+      <c r="A5" s="37">
         <v>2</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="38">
         <f t="shared" ref="F5:F6" si="0">INDEX($K$9:$K$14,MATCH(B5,$A$9:$A$14,0))</f>
         <v>2.8</v>
       </c>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
     </row>
     <row r="6" spans="1:16" ht="46.05" customHeight="1">
-      <c r="A6" s="45">
+      <c r="A6" s="37">
         <v>3</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="38">
         <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
     </row>
     <row r="8" spans="1:16" ht="42" customHeight="1">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="H8" s="43" t="s">
+      <c r="H8" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="J8" s="43" t="s">
+      <c r="J8" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="K8" s="43" t="s">
+      <c r="K8" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="L8" s="43" t="s">
+      <c r="L8" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="M8" s="43" t="s">
+      <c r="M8" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="N8" s="43" t="s">
+      <c r="N8" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="O8" s="43" t="s">
+      <c r="O8" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="P8" s="43" t="s">
+      <c r="P8" s="36" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="72" customHeight="1">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="48">
+      <c r="B9" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2024,SalesData[商品カテゴリ],$A9)</f>
         <v>1561802000</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2025,SalesData[商品カテゴリ],$A9)</f>
         <v>2032689000</v>
       </c>
-      <c r="D9" s="49">
+      <c r="D9" s="41">
         <f>IFERROR(C9/B9-1,"")</f>
         <v>0.30150236713744771</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="41">
         <f>IFERROR((C9-SUMIFS(SalesData[売上原価],SalesData[年],2025,SalesData[商品カテゴリ],$A9))/C9,"")</f>
         <v>0.2651192582829936</v>
       </c>
-      <c r="F9" s="50">
+      <c r="F9" s="42">
         <f>IF(_xlfn.RANK.EQ(C9,$C$9:$C$14)=1,5,IF(_xlfn.RANK.EQ(C9,$C$9:$C$14)=2,4,IF(_xlfn.RANK.EQ(C9,$C$9:$C$14)=3,3,IF(_xlfn.RANK.EQ(C9,$C$9:$C$14)=4,2,1))))</f>
         <v>5</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="42">
         <f>IF(D9&gt;=20%,5,IF(D9&gt;=10%,4,IF(D9&gt;=5%,3,IF(D9&gt;=0%,2,1))))</f>
         <v>5</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="42">
         <f>IF(E9&gt;=55%,5,IF(E9&gt;=45%,4,IF(E9&gt;=40%,3,IF(E9&gt;=30%,2,1))))</f>
         <v>1</v>
       </c>
-      <c r="I9" s="50">
+      <c r="I9" s="42">
         <v>5</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9" s="42">
         <v>2</v>
       </c>
-      <c r="K9" s="51">
+      <c r="K9" s="43">
         <f>ROUND(AVERAGE(F9:J9),1)</f>
         <v>3.6</v>
       </c>
-      <c r="L9" s="51" t="s">
+      <c r="L9" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="M9" s="51">
+      <c r="M9" s="43">
         <f>_xlfn.RANK.EQ(K9,$K$9:$K$14)</f>
         <v>2</v>
       </c>
-      <c r="N9" s="52" t="str">
+      <c r="N9" s="35" t="str">
         <f>"2025年売上 "&amp;TEXT(C9/100000000,"0.00")&amp;"億円、前年比 "&amp;TEXT(D9,"0.0%")&amp;"、粗利率 "&amp;TEXT(E9,"0.0%")</f>
         <v>2025年売上 20.33億円、前年比 30.2%、粗利率 26.5%</v>
       </c>
-      <c r="O9" s="52" t="s">
+      <c r="O9" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="P9" s="52" t="s">
+      <c r="P9" s="35" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="72" customHeight="1">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2024,SalesData[商品カテゴリ],$A10)</f>
         <v>1204184000</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2025,SalesData[商品カテゴリ],$A10)</f>
         <v>1269723000</v>
       </c>
-      <c r="D10" s="49">
+      <c r="D10" s="41">
         <f t="shared" ref="D10:D14" si="1">IFERROR(C10/B10-1,"")</f>
         <v>5.4426067777017417E-2</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="41">
         <f>IFERROR((C10-SUMIFS(SalesData[売上原価],SalesData[年],2025,SalesData[商品カテゴリ],$A10))/C10,"")</f>
         <v>0.40185300258402817</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="42">
         <f t="shared" ref="F10:F14" si="2">IF(_xlfn.RANK.EQ(C10,$C$9:$C$14)=1,5,IF(_xlfn.RANK.EQ(C10,$C$9:$C$14)=2,4,IF(_xlfn.RANK.EQ(C10,$C$9:$C$14)=3,3,IF(_xlfn.RANK.EQ(C10,$C$9:$C$14)=4,2,1))))</f>
         <v>4</v>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="42">
         <f t="shared" ref="G10:G14" si="3">IF(D10&gt;=20%,5,IF(D10&gt;=10%,4,IF(D10&gt;=5%,3,IF(D10&gt;=0%,2,1))))</f>
         <v>3</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="42">
         <f t="shared" ref="H10:H14" si="4">IF(E10&gt;=55%,5,IF(E10&gt;=45%,4,IF(E10&gt;=40%,3,IF(E10&gt;=30%,2,1))))</f>
         <v>3</v>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="42">
         <v>3</v>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="42">
         <v>3</v>
       </c>
-      <c r="K10" s="51">
+      <c r="K10" s="43">
         <f t="shared" ref="K10:K14" si="5">ROUND(AVERAGE(F10:J10),1)</f>
         <v>3.2</v>
       </c>
-      <c r="L10" s="51" t="s">
+      <c r="L10" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="M10" s="51">
+      <c r="M10" s="43">
         <f t="shared" ref="M10:M14" si="6">_xlfn.RANK.EQ(K10,$K$9:$K$14)</f>
         <v>3</v>
       </c>
-      <c r="N10" s="52" t="str">
+      <c r="N10" s="35" t="str">
         <f t="shared" ref="N10:N14" si="7">"2025年売上 "&amp;TEXT(C10/100000000,"0.00")&amp;"億円、前年比 "&amp;TEXT(D10,"0.0%")&amp;"、粗利率 "&amp;TEXT(E10,"0.0%")</f>
         <v>2025年売上 12.70億円、前年比 5.4%、粗利率 40.2%</v>
       </c>
-      <c r="O10" s="52" t="s">
+      <c r="O10" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="P10" s="52" t="s">
+      <c r="P10" s="35" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="72" customHeight="1">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="48">
+      <c r="B11" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2024,SalesData[商品カテゴリ],$A11)</f>
         <v>715823000</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2025,SalesData[商品カテゴリ],$A11)</f>
         <v>737050000</v>
       </c>
-      <c r="D11" s="49">
+      <c r="D11" s="41">
         <f t="shared" si="1"/>
         <v>2.9653978707026685E-2</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="41">
         <f>IFERROR((C11-SUMIFS(SalesData[売上原価],SalesData[年],2025,SalesData[商品カテゴリ],$A11))/C11,"")</f>
         <v>0.46681636252628722</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="42">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="42">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="42">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="42">
         <v>2</v>
       </c>
-      <c r="J11" s="50">
+      <c r="J11" s="42">
         <v>2</v>
       </c>
-      <c r="K11" s="51">
+      <c r="K11" s="43">
         <f t="shared" si="5"/>
         <v>2.6</v>
       </c>
-      <c r="L11" s="51" t="s">
+      <c r="L11" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="43">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="N11" s="52" t="str">
+      <c r="N11" s="35" t="str">
         <f t="shared" si="7"/>
         <v>2025年売上 7.37億円、前年比 3.0%、粗利率 46.7%</v>
       </c>
-      <c r="O11" s="52" t="s">
+      <c r="O11" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="P11" s="52" t="s">
+      <c r="P11" s="35" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="72" customHeight="1">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2024,SalesData[商品カテゴリ],$A12)</f>
         <v>560913000</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2025,SalesData[商品カテゴリ],$A12)</f>
         <v>694214000</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="41">
         <f t="shared" si="1"/>
         <v>0.23765004555073599</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="41">
         <f>IFERROR((C12-SUMIFS(SalesData[売上原価],SalesData[年],2025,SalesData[商品カテゴリ],$A12))/C12,"")</f>
         <v>0.51746867680571118</v>
       </c>
-      <c r="F12" s="50">
+      <c r="F12" s="42">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="42">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="42">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12" s="42">
         <v>5</v>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="42">
         <v>3</v>
       </c>
-      <c r="K12" s="51">
+      <c r="K12" s="43">
         <f t="shared" si="5"/>
         <v>3.8</v>
       </c>
-      <c r="L12" s="51" t="s">
+      <c r="L12" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="43">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N12" s="52" t="str">
+      <c r="N12" s="35" t="str">
         <f t="shared" si="7"/>
         <v>2025年売上 6.94億円、前年比 23.8%、粗利率 51.7%</v>
       </c>
-      <c r="O12" s="52" t="s">
+      <c r="O12" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="P12" s="52" t="s">
+      <c r="P12" s="35" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="72" customHeight="1">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2024,SalesData[商品カテゴリ],$A13)</f>
         <v>524187000</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="40">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2025,SalesData[商品カテゴリ],$A13)</f>
         <v>574936000</v>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="41">
         <f t="shared" si="1"/>
         <v>9.6814686361928137E-2</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="41">
         <f>IFERROR((C13-SUMIFS(SalesData[売上原価],SalesData[年],2025,SalesData[商品カテゴリ],$A13))/C13,"")</f>
         <v>0.62796902611768957</v>
       </c>
-      <c r="F13" s="50">
+      <c r="F13" s="42">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="42">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="42">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13" s="42">
         <v>2</v>
       </c>
-      <c r="J13" s="50">
+      <c r="J13" s="42">
         <v>3</v>
       </c>
-      <c r="K13" s="51">
+      <c r="K13" s="43">
         <f t="shared" si="5"/>
         <v>2.8</v>
       </c>
-      <c r="L13" s="51" t="s">
+      <c r="L13" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="M13" s="51">
+      <c r="M13" s="43">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="N13" s="52" t="str">
+      <c r="N13" s="35" t="str">
         <f t="shared" si="7"/>
         <v>2025年売上 5.75億円、前年比 9.7%、粗利率 62.8%</v>
       </c>
-      <c r="O13" s="52" t="s">
+      <c r="O13" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="P13" s="52" t="s">
+      <c r="P13" s="35" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="72" customHeight="1">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="45">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2024,SalesData[商品カテゴリ],$A14)</f>
         <v>338972000</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="45">
         <f>SUMIFS(SalesData[売上金額],SalesData[年],2025,SalesData[商品カテゴリ],$A14)</f>
         <v>342432000</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="46">
         <f t="shared" si="1"/>
         <v>1.0207332759047949E-2</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="46">
         <f>IFERROR((C14-SUMIFS(SalesData[売上原価],SalesData[年],2025,SalesData[商品カテゴリ],$A14))/C14,"")</f>
         <v>0.43124182319409399</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="47">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="47">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H14" s="47">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="I14" s="56">
+      <c r="I14" s="47">
         <v>2</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="47">
         <v>2</v>
       </c>
-      <c r="K14" s="57">
+      <c r="K14" s="48">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="L14" s="57" t="s">
+      <c r="L14" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="M14" s="57">
+      <c r="M14" s="48">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="N14" s="58" t="str">
+      <c r="N14" s="49" t="str">
         <f t="shared" si="7"/>
         <v>2025年売上 3.42億円、前年比 1.0%、粗利率 43.1%</v>
       </c>
-      <c r="O14" s="58" t="s">
+      <c r="O14" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="P14" s="58" t="s">
+      <c r="P14" s="49" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
     </row>
     <row r="16" spans="1:16" ht="42" customHeight="1">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="86" t="s">
         <v>249</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="86"/>
+      <c r="P16" s="86"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
     </row>
     <row r="18" spans="1:16" ht="52.05" customHeight="1">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="87" t="s">
         <v>250</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
+      <c r="O18" s="87"/>
+      <c r="P18" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -85302,828 +85292,816 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="55" t="s">
         <v>252</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="60"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="50"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="60"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="50"/>
     </row>
     <row r="3" spans="1:15" ht="20" customHeight="1">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="60"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="50"/>
     </row>
     <row r="4" spans="1:15" ht="15">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="60"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="50"/>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="73" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="71" t="s">
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="59" t="s">
         <v>255</v>
       </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="79" t="s">
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="60"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="50"/>
     </row>
     <row r="6" spans="1:15" ht="26" customHeight="1">
-      <c r="A6" s="69">
+      <c r="A6" s="61">
         <f>カテゴリ別集計!C10/100000000</f>
         <v>56.510440000000003</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="75">
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="67">
         <f>カテゴリ別集計!F10</f>
         <v>0.15189178049773333</v>
       </c>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="69">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="61">
         <f>(SUMIFS(SalesData[売上金額],SalesData[年],2025)-SUMIFS(SalesData[売上原価],SalesData[年],2025))/100000000</f>
         <v>22.611609999999999</v>
       </c>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="82" t="str">
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="74" t="str">
         <f>TEXT((SUMIFS(SalesData[売上金額],SalesData[年],2025)-SUMIFS(SalesData[売上原価],SalesData[年],2025))/SUMIFS(SalesData[売上金額],SalesData[年],2025),"0.0%")&amp;" / "&amp;TEXT(((SUMIFS(SalesData[売上金額],SalesData[年],2025)-SUMIFS(SalesData[売上原価],SalesData[年],2025))/SUMIFS(SalesData[売上金額],SalesData[年],2025)-(SUMIFS(SalesData[売上金額],SalesData[年],2024)-SUMIFS(SalesData[売上原価],SalesData[年],2024))/SUMIFS(SalesData[売上金額],SalesData[年],2024))*100,"0.0")&amp;"pt"</f>
         <v>40.0% / -0.6pt</v>
       </c>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="60"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="50"/>
     </row>
     <row r="7" spans="1:15" ht="26" customHeight="1">
-      <c r="A7" s="70"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="60"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="50"/>
     </row>
     <row r="8" spans="1:15" ht="15">
-      <c r="A8" s="61"/>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="61"/>
-      <c r="O8" s="60"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="50"/>
     </row>
     <row r="9" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="53" t="s">
         <v>257</v>
       </c>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="88" t="s">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="53" t="s">
         <v>258</v>
       </c>
-      <c r="I9" s="89"/>
-      <c r="J9" s="89"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="89"/>
-      <c r="M9" s="89"/>
-      <c r="N9" s="89"/>
-      <c r="O9" s="60"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="50"/>
     </row>
     <row r="10" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A10" s="62" t="str">
+      <c r="A10" s="52" t="str">
         <f>"[社内] 売上は49.06億円から56.51億円へ15.2%増、粗利は19.95億円から22.61億円へ13.4%増。粗利率は40.7%から40.0%へ0.6pt低下。"&amp;CHAR(10)&amp;"[Web] 国内市場は2024年8兆5,010億円、前年比1.7%増だが、人口減少下では微増基調。ECと実店舗の連携が成長条件。"&amp;CHAR(10)&amp;"[リスク] 増収が値引き・商品ミックス悪化を通じて利益率低下を招く。"&amp;CHAR(10)&amp;"[要確認] SKU別の値引率、仕入単価、在庫回転、チャネル別粗利。"</f>
         <v>[社内] 売上は49.06億円から56.51億円へ15.2%増、粗利は19.95億円から22.61億円へ13.4%増。粗利率は40.7%から40.0%へ0.6pt低下。
 [Web] 国内市場は2024年8兆5,010億円、前年比1.7%増だが、人口減少下では微増基調。ECと実店舗の連携が成長条件。
 [リスク] 増収が値引き・商品ミックス悪化を通じて利益率低下を招く。
 [要確認] SKU別の値引率、仕入単価、在庫回転、チャネル別粗利。</v>
       </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62" t="str">
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52" t="str">
         <f>"[社内] 売上成長15.2%に対し粗利成長13.4%。最大カテゴリのスポーツウェアは成長30.2%だが粗利率26.5%。"&amp;CHAR(10)&amp;"[Web] 原材料費・物流費・人件費の上昇が続き、販売数量より単価と在庫効率が利益を左右する。"&amp;CHAR(10)&amp;"[リスク] 低粗利カテゴリの拡大で全社粗利率がさらに低下。バブルチャートでもスポーツは右端だが下段。"&amp;CHAR(10)&amp;"[要確認] スポーツの価格弾力性、競合価格、原価低減余地、販促ROI。"</f>
         <v>[社内] 売上成長15.2%に対し粗利成長13.4%。最大カテゴリのスポーツウェアは成長30.2%だが粗利率26.5%。
 [Web] 原材料費・物流費・人件費の上昇が続き、販売数量より単価と在庫効率が利益を左右する。
 [リスク] 低粗利カテゴリの拡大で全社粗利率がさらに低下。バブルチャートでもスポーツは右端だが下段。
 [要確認] スポーツの価格弾力性、競合価格、原価低減余地、販促ROI。</v>
       </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="60"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="50"/>
     </row>
     <row r="11" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="62"/>
-      <c r="M11" s="62"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="60"/>
+      <c r="A11" s="52"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="50"/>
     </row>
     <row r="12" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="62"/>
-      <c r="L12" s="62"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="60"/>
+      <c r="A12" s="52"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="50"/>
     </row>
     <row r="13" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="60"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="50"/>
     </row>
     <row r="14" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="60"/>
+      <c r="A14" s="52"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="50"/>
     </row>
     <row r="15" spans="1:15" ht="15">
-      <c r="A15" s="61"/>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="60"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="50"/>
     </row>
     <row r="16" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A16" s="88" t="s">
+      <c r="A16" s="53" t="s">
         <v>259</v>
       </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="88" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="89"/>
-      <c r="M16" s="89"/>
-      <c r="N16" s="89"/>
-      <c r="O16" s="60"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="50"/>
     </row>
     <row r="17" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A17" s="62" t="str">
+      <c r="A17" s="52" t="str">
         <f>"[社内] サステナブルライン: 売上6.94億円、成長23.8%、粗利率51.7%。バブルチャートの右上領域。プレミアムビジネス: 売上5.75億円、成長9.7%、粗利率62.8%で最高収益性。"&amp;CHAR(10)&amp;"[Web] 循環経済は国家戦略で、衣類廃棄量を2030年度までに25%削減する目標。スーツ市場は量販縮小の一方、オーダー・高付加価値・機能性が成長機会。"&amp;CHAR(10)&amp;"[リスク] サステナブル素材コストと認証負担、プレミアム市場総量の縮小。"&amp;CHAR(10)&amp;"[要確認] 認証・原料追跡、価格受容性、オーダー運用能力、旗艦店別需要。"</f>
         <v>[社内] サステナブルライン: 売上6.94億円、成長23.8%、粗利率51.7%。バブルチャートの右上領域。プレミアムビジネス: 売上5.75億円、成長9.7%、粗利率62.8%で最高収益性。
 [Web] 循環経済は国家戦略で、衣類廃棄量を2030年度までに25%削減する目標。スーツ市場は量販縮小の一方、オーダー・高付加価値・機能性が成長機会。
 [リスク] サステナブル素材コストと認証負担、プレミアム市場総量の縮小。
 [要確認] 認証・原料追跡、価格受容性、オーダー運用能力、旗艦店別需要。</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62" t="str">
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52" t="str">
         <f>"[社内] スポーツウェア: 売上20.33億円、成長30.2%で最大の成長源。一方、粗利率26.5%は全カテゴリ最低。"&amp;CHAR(10)&amp;"[Web] 健康志向、アスレジャー、ECが国内需要を支える一方、合成繊維・物流コストと低価格競争が収益を圧迫。"&amp;CHAR(10)&amp;"[リスク] 売上拡大だけを追うと全社粗利率を希薄化。"&amp;CHAR(10)&amp;"[要確認] 粗利率改善の数値目標、値引き上限、SKU削減、女性向け・高機能商品の構成比。"</f>
         <v>[社内] スポーツウェア: 売上20.33億円、成長30.2%で最大の成長源。一方、粗利率26.5%は全カテゴリ最低。
 [Web] 健康志向、アスレジャー、ECが国内需要を支える一方、合成繊維・物流コストと低価格競争が収益を圧迫。
 [リスク] 売上拡大だけを追うと全社粗利率を希薄化。
 [要確認] 粗利率改善の数値目標、値引き上限、SKU削減、女性向け・高機能商品の構成比。</v>
       </c>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="62"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="60"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="50"/>
     </row>
     <row r="18" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="60"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="50"/>
     </row>
     <row r="19" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="60"/>
+      <c r="A19" s="52"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="50"/>
     </row>
     <row r="20" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A20" s="62"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="60"/>
+      <c r="A20" s="52"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="50"/>
     </row>
     <row r="21" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A21" s="62"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="60"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="50"/>
     </row>
     <row r="22" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A22" s="62"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="60"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="50"/>
     </row>
     <row r="23" spans="1:15" ht="15">
-      <c r="A23" s="61"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="60"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="50"/>
     </row>
     <row r="24" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="88" t="s">
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="89"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="60"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="50"/>
     </row>
     <row r="25" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A25" s="62" t="str">
+      <c r="A25" s="52" t="str">
         <f>"[社内] 九州を最優先: 売上18.26億円、成長31.9%、粗利率42.7%。次点は関西: 売上23.79億円、粗利率44.1%。北海道・東北は成長17.0%だが粗利率39.6%のため選択投資。"&amp;CHAR(10)&amp;"[Web] 2025年訪日客は4,268万人。観光・買物需要を取り込む店舗とECの連携が重要。"&amp;CHAR(10)&amp;"[リスク] 九州への集中、繁閑差、人員・在庫不足。"&amp;CHAR(10)&amp;"[要確認] 店舗別成長、面積生産性、インバウンド購買、追加在庫の粗利効果。"</f>
         <v>[社内] 九州を最優先: 売上18.26億円、成長31.9%、粗利率42.7%。次点は関西: 売上23.79億円、粗利率44.1%。北海道・東北は成長17.0%だが粗利率39.6%のため選択投資。
 [Web] 2025年訪日客は4,268万人。観光・買物需要を取り込む店舗とECの連携が重要。
 [リスク] 九州への集中、繁閑差、人員・在庫不足。
 [要確認] 店舗別成長、面積生産性、インバウンド購買、追加在庫の粗利効果。</v>
       </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62" t="str">
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52" t="str">
         <f>"[社内] 1位 沖縄: 市場480億円、成長14.2%、インバウンド指数98、競合11。2位 京都: 860億円、4.6%、指数92。3位 千葉: 1,240億円、2.8%、関東既存網との補完性。"&amp;CHAR(10)&amp;"[Web] JNTO・観光庁は都道府県別訪問・宿泊・消費を継続公表。沖縄県も入域観光客を月次管理しており、観光需要検証が可能。"&amp;CHAR(10)&amp;"[リスク] 沖縄の物流・季節性、京都の高賃料・競争、千葉の既存店カニバリ。"&amp;CHAR(10)&amp;"[要確認] 商圏別売上予測、賃料、人件費、物流費、競合距離、投資回収期間。"</f>
         <v>[社内] 1位 沖縄: 市場480億円、成長14.2%、インバウンド指数98、競合11。2位 京都: 860億円、4.6%、指数92。3位 千葉: 1,240億円、2.8%、関東既存網との補完性。
 [Web] JNTO・観光庁は都道府県別訪問・宿泊・消費を継続公表。沖縄県も入域観光客を月次管理しており、観光需要検証が可能。
 [リスク] 沖縄の物流・季節性、京都の高賃料・競争、千葉の既存店カニバリ。
 [要確認] 商圏別売上予測、賃料、人件費、物流費、競合距離、投資回収期間。</v>
       </c>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="62"/>
-      <c r="M25" s="62"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="60"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="50"/>
     </row>
     <row r="26" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A26" s="62"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="60"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="50"/>
     </row>
     <row r="27" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A27" s="62"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="60"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="50"/>
     </row>
     <row r="28" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A28" s="62"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="60"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="50"/>
     </row>
     <row r="29" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A29" s="62"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="62"/>
-      <c r="M29" s="62"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="60"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="52"/>
+      <c r="O29" s="50"/>
     </row>
     <row r="30" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A30" s="62"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="62"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="60"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="50"/>
     </row>
     <row r="31" spans="1:15" ht="15">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="60"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="50"/>
     </row>
     <row r="32" spans="1:15" ht="22.05" customHeight="1">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="89"/>
-      <c r="M32" s="89"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="60"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="54"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="50"/>
     </row>
     <row r="33" spans="1:15" ht="20" customHeight="1">
-      <c r="A33" s="62" t="s">
+      <c r="A33" s="52" t="s">
         <v>264</v>
       </c>
-      <c r="B33" s="62"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
-      <c r="M33" s="62"/>
-      <c r="N33" s="62"/>
-      <c r="O33" s="60"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="50"/>
     </row>
     <row r="34" spans="1:15" ht="20" customHeight="1">
-      <c r="A34" s="62"/>
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="62"/>
-      <c r="O34" s="60"/>
+      <c r="A34" s="52"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="50"/>
     </row>
     <row r="35" spans="1:15" ht="20" customHeight="1">
-      <c r="A35" s="62"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="62"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="60"/>
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="50"/>
     </row>
     <row r="36" spans="1:15" ht="20" customHeight="1">
-      <c r="A36" s="62"/>
-      <c r="B36" s="62"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="62"/>
-      <c r="O36" s="60"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="50"/>
     </row>
     <row r="37" spans="1:15" ht="20" customHeight="1">
-      <c r="A37" s="62"/>
-      <c r="B37" s="62"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="62"/>
-      <c r="N37" s="62"/>
-      <c r="O37" s="60"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="50"/>
     </row>
     <row r="38" spans="1:15" ht="20" customHeight="1">
-      <c r="A38" s="62"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="62"/>
-      <c r="O38" s="60"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="50"/>
     </row>
     <row r="39" spans="1:15" ht="20" customHeight="1">
-      <c r="A39" s="62"/>
-      <c r="B39" s="62"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="62"/>
-      <c r="N39" s="62"/>
-      <c r="O39" s="60"/>
+      <c r="A39" s="52"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="50"/>
     </row>
     <row r="40" spans="1:15" ht="15">
-      <c r="A40" s="61"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="61"/>
-      <c r="O40" s="60"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+      <c r="L40" s="51"/>
+      <c r="M40" s="51"/>
+      <c r="N40" s="51"/>
+      <c r="O40" s="50"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
-      <c r="A41" s="62" t="s">
+      <c r="A41" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="B41" s="62"/>
-      <c r="C41" s="62"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="62"/>
-      <c r="M41" s="62"/>
-      <c r="N41" s="62"/>
-      <c r="O41" s="60"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="52"/>
+      <c r="N41" s="52"/>
+      <c r="O41" s="50"/>
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1">
-      <c r="A42" s="62"/>
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="62"/>
-      <c r="N42" s="62"/>
-      <c r="O42" s="60"/>
+      <c r="A42" s="52"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="50"/>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43" s="60"/>
-      <c r="B43" s="60"/>
-      <c r="C43" s="60"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="60"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="60"/>
-      <c r="H43" s="60"/>
-      <c r="I43" s="60"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="60"/>
-      <c r="O43" s="60"/>
+      <c r="A43" s="50"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="50"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="50"/>
+      <c r="O43" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A41:N42"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:G30"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="H25:N30"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="A33:N39"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G14"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="H10:N14"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A17:G22"/>
     <mergeCell ref="H16:N16"/>
     <mergeCell ref="H17:N22"/>
@@ -86137,6 +86115,18 @@
     <mergeCell ref="G6:I7"/>
     <mergeCell ref="J5:N5"/>
     <mergeCell ref="J6:N7"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G14"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="H10:N14"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A41:N42"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G30"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="H25:N30"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="A33:N39"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
